--- a/data/generated/plots/ClassifiersAccuracyFake.xlsx
+++ b/data/generated/plots/ClassifiersAccuracyFake.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L5"/>
+  <dimension ref="A1:L8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -561,7 +561,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.843</v>
+        <v>0.841</v>
       </c>
       <c r="D4" t="n">
         <v>0.598</v>
@@ -572,22 +572,22 @@
       <c r="F4" t="n">
         <v>0.897</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" t="n">
         <v>280</v>
       </c>
       <c r="H4" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>0.105</v>
+        <v>0.076</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0.057</v>
       </c>
       <c r="J4" t="n">
-        <v>0.522</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>0.473</v>
-      </c>
-      <c r="L4" s="4" t="n">
+        <v>0.484</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.471</v>
+      </c>
+      <c r="L4" t="n">
         <v>1</v>
       </c>
     </row>
@@ -600,35 +600,155 @@
           <t>MobileNet_v2</t>
         </is>
       </c>
-      <c r="C5" s="4" t="n">
-        <v>0.863</v>
+      <c r="C5" t="n">
+        <v>0.868</v>
       </c>
       <c r="D5" s="4" t="n">
         <v>0.638</v>
       </c>
-      <c r="E5" s="4" t="n">
-        <v>0.987</v>
-      </c>
-      <c r="F5" s="4" t="n">
+      <c r="E5" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="F5" t="n">
         <v>0.919</v>
       </c>
       <c r="G5" t="n">
         <v>259</v>
       </c>
-      <c r="H5" s="4" t="n">
-        <v>0.157</v>
+      <c r="H5" t="n">
+        <v>0.243</v>
       </c>
       <c r="I5" t="n">
-        <v>0.095</v>
-      </c>
-      <c r="J5" s="4" t="n">
-        <v>0.577</v>
+        <v>0.053</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0.759</v>
       </c>
       <c r="K5" t="n">
-        <v>0.472</v>
-      </c>
-      <c r="L5" t="n">
+        <v>0.422</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>2</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Resnet34</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>0.871</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.625</v>
+      </c>
+      <c r="E6" t="n">
+        <v>0.987</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.915</v>
+      </c>
+      <c r="G6" s="4" t="n">
+        <v>283</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0.068</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0.549</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>0.529</v>
+      </c>
+      <c r="L6" t="n">
         <v>1</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>3</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>SqueezeNet1_1</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>0.739</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.554</v>
+      </c>
+      <c r="E7" t="n">
+        <v>0.972</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="G7" t="n">
+        <v>275</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0.203</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0.064</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0.762</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.412</v>
+      </c>
+      <c r="L7" t="n">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>4</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>VGG13</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="n">
+        <v>0.906</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.607</v>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>0.995</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="G8" t="n">
+        <v>280</v>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>0.253</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>0.104</v>
+      </c>
+      <c r="J8" s="4" t="n">
+        <v>0.8129999999999999</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.408</v>
+      </c>
+      <c r="L8" t="n">
+        <v>18</v>
       </c>
     </row>
   </sheetData>
